--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The Haddon 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The Haddon" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21552,239 +21590,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Haddon - The Haddon 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>The Haddon 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>453 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>446 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R4" s="19" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S4" s="19" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T4" s="19" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U4" s="19" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V4" s="19" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
-$1,093万
+$1093万
 $26,200/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
-$1,077万
+$1077万
 $29,200/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $795万
@@ -21792,15 +21830,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
-$1,143万
+$1143万
 $27,800/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $731万
@@ -21808,7 +21846,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $670万
@@ -21816,7 +21854,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $673万
@@ -21824,7 +21862,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $673万
@@ -21832,7 +21870,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $687万
@@ -21840,7 +21878,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $668万
@@ -21848,7 +21886,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $708万
@@ -21856,7 +21894,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $716万
@@ -21864,15 +21902,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 642呎 (3房)
-$2,183万
+$2183万
 $34,000/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>P | 255呎 (1房)
 招标单位
@@ -21880,7 +21918,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>Q | 384呎 (2房)
 招标单位
@@ -21888,7 +21926,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q6" s="17" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>R | 384呎 (2房)
 招标单位
@@ -21896,19 +21934,19 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="18" t="inlineStr"/>
-      <c r="S6" s="18" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr"/>
-      <c r="U6" s="18" t="inlineStr"/>
-      <c r="V6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="R5" s="22" t="inlineStr"/>
+      <c r="S5" s="22" t="inlineStr"/>
+      <c r="T5" s="22" t="inlineStr"/>
+      <c r="U5" s="22" t="inlineStr"/>
+      <c r="V5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $862万
@@ -21916,7 +21954,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $830万
@@ -21924,7 +21962,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $564万
@@ -21932,7 +21970,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $843万
@@ -21940,7 +21978,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $547万
@@ -21948,7 +21986,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $495万
@@ -21956,7 +21994,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $523万
@@ -21964,7 +22002,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $518万
@@ -21972,7 +22010,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $518万
@@ -21980,7 +22018,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $523万
@@ -21988,7 +22026,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $520万
@@ -21996,7 +22034,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $522万
@@ -22004,7 +22042,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 251呎 (1房)
 $533万
@@ -22012,7 +22050,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O6" s="21" t="inlineStr">
         <is>
           <t>P | 568呎 (3房)
 招标单位
@@ -22020,7 +22058,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>Q | 317呎 (2房)
 招标单位
@@ -22028,7 +22066,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q7" s="17" t="inlineStr">
+      <c r="Q6" s="21" t="inlineStr">
         <is>
           <t>R | 384呎 (2房)
 招标单位
@@ -22036,7 +22074,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t>S | 384呎 (2房)
 招标单位
@@ -22044,18 +22082,18 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr"/>
-      <c r="T7" s="18" t="inlineStr"/>
-      <c r="U7" s="18" t="inlineStr"/>
-      <c r="V7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr"/>
+      <c r="T6" s="22" t="inlineStr"/>
+      <c r="U6" s="22" t="inlineStr"/>
+      <c r="V6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $857万
@@ -22063,7 +22101,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $825万
@@ -22071,7 +22109,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $561万
@@ -22079,7 +22117,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $838万
@@ -22087,7 +22125,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $553万
@@ -22095,7 +22133,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $492万
@@ -22103,7 +22141,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $520万
@@ -22111,7 +22149,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $515万
@@ -22119,7 +22157,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $506万
@@ -22127,7 +22165,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $503万
@@ -22135,7 +22173,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $528万
@@ -22143,7 +22181,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $537万
@@ -22151,7 +22189,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $530万
@@ -22159,7 +22197,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $609万
@@ -22167,7 +22205,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="P8" s="16" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $843万
@@ -22175,7 +22213,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="Q8" s="16" t="inlineStr">
+      <c r="Q7" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $669万
@@ -22183,7 +22221,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="R8" s="16" t="inlineStr">
+      <c r="R7" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $499万
@@ -22191,7 +22229,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="S8" s="16" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $532万
@@ -22199,7 +22237,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T8" s="16" t="inlineStr">
+      <c r="T7" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $557万
@@ -22207,7 +22245,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U8" s="16" t="inlineStr">
+      <c r="U7" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $537万
@@ -22215,7 +22253,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V8" s="16" t="inlineStr">
+      <c r="V7" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $562万
@@ -22224,13 +22262,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $855万
@@ -22238,7 +22276,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $821万
@@ -22246,7 +22284,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $557万
@@ -22254,7 +22292,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $847万
@@ -22262,7 +22300,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $551万
@@ -22270,7 +22308,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $499万
@@ -22278,7 +22316,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $527万
@@ -22286,7 +22324,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $522万
@@ -22294,7 +22332,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $505万
@@ -22302,7 +22340,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $516万
@@ -22310,7 +22348,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $525万
@@ -22318,7 +22356,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $534万
@@ -22326,7 +22364,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $527万
@@ -22334,7 +22372,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $602万
@@ -22342,7 +22380,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="P9" s="16" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $838万
@@ -22350,7 +22388,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="Q9" s="16" t="inlineStr">
+      <c r="Q8" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $677万
@@ -22358,7 +22396,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="R9" s="16" t="inlineStr">
+      <c r="R8" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $496万
@@ -22366,7 +22404,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="S9" s="16" t="inlineStr">
+      <c r="S8" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $529万
@@ -22374,7 +22412,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T9" s="16" t="inlineStr">
+      <c r="T8" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $554万
@@ -22382,7 +22420,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U9" s="16" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $534万
@@ -22390,7 +22428,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V9" s="16" t="inlineStr">
+      <c r="V8" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $559万
@@ -22399,13 +22437,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $852万
@@ -22413,7 +22451,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $816万
@@ -22421,7 +22459,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $554万
@@ -22429,7 +22467,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $828万
@@ -22437,7 +22475,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $549万
@@ -22445,7 +22483,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $498万
@@ -22453,7 +22491,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $525万
@@ -22461,7 +22499,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $520万
@@ -22469,7 +22507,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $495万
@@ -22477,7 +22515,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $511万
@@ -22485,7 +22523,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $522万
@@ -22493,7 +22531,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $530万
@@ -22501,7 +22539,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $524万
@@ -22509,7 +22547,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $599万
@@ -22517,7 +22555,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $833万
@@ -22525,7 +22563,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="Q10" s="16" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $675万
@@ -22533,7 +22571,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="R10" s="16" t="inlineStr">
+      <c r="R9" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $495万
@@ -22541,7 +22579,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S10" s="16" t="inlineStr">
+      <c r="S9" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $527万
@@ -22549,7 +22587,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T10" s="16" t="inlineStr">
+      <c r="T9" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $550万
@@ -22557,7 +22595,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U10" s="16" t="inlineStr">
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $531万
@@ -22565,7 +22603,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V10" s="16" t="inlineStr">
+      <c r="V9" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $545万
@@ -22574,13 +22612,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $850万
@@ -22588,7 +22626,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $814万
@@ -22596,7 +22634,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $552万
@@ -22604,7 +22642,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $826万
@@ -22612,7 +22650,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $548万
@@ -22620,7 +22658,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $496万
@@ -22628,7 +22666,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $524万
@@ -22636,7 +22674,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $519万
@@ -22644,7 +22682,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $494万
@@ -22652,7 +22690,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $499万
@@ -22660,7 +22698,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $509万
@@ -22668,7 +22706,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $511万
@@ -22676,7 +22714,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $522万
@@ -22684,7 +22722,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $587万
@@ -22692,7 +22730,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="P11" s="16" t="inlineStr">
+      <c r="P10" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $831万
@@ -22700,7 +22738,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q11" s="16" t="inlineStr">
+      <c r="Q10" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $673万
@@ -22708,7 +22746,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="R11" s="16" t="inlineStr">
+      <c r="R10" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $493万
@@ -22716,7 +22754,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S11" s="16" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $526万
@@ -22724,7 +22762,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T11" s="16" t="inlineStr">
+      <c r="T10" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $547万
@@ -22732,7 +22770,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U11" s="16" t="inlineStr">
+      <c r="U10" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $528万
@@ -22740,7 +22778,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V11" s="16" t="inlineStr">
+      <c r="V10" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $542万
@@ -22749,13 +22787,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $847万
@@ -22763,7 +22801,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $811万
@@ -22771,7 +22809,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $551万
@@ -22779,7 +22817,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $824万
@@ -22787,7 +22825,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $546万
@@ -22795,7 +22833,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $486万
@@ -22803,7 +22841,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $522万
@@ -22811,7 +22849,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $517万
@@ -22819,7 +22857,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $492万
@@ -22827,7 +22865,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $497万
@@ -22835,7 +22873,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $519万
@@ -22843,7 +22881,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $510万
@@ -22851,7 +22889,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $521万
@@ -22859,7 +22897,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $599万
@@ -22867,7 +22905,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="P12" s="16" t="inlineStr">
+      <c r="P11" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $857万
@@ -22875,7 +22913,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="Q12" s="16" t="inlineStr">
+      <c r="Q11" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $660万
@@ -22883,7 +22921,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="R12" s="16" t="inlineStr">
+      <c r="R11" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $492万
@@ -22891,7 +22929,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S12" s="16" t="inlineStr">
+      <c r="S11" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $524万
@@ -22899,7 +22937,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T12" s="16" t="inlineStr">
+      <c r="T11" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $544万
@@ -22907,7 +22945,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U12" s="16" t="inlineStr">
+      <c r="U11" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $525万
@@ -22915,7 +22953,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V12" s="16" t="inlineStr">
+      <c r="V11" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $539万
@@ -22924,13 +22962,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $828万
@@ -22938,7 +22976,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $809万
@@ -22946,7 +22984,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $549万
@@ -22954,7 +22992,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $821万
@@ -22962,7 +23000,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $535万
@@ -22970,7 +23008,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $485万
@@ -22978,7 +23016,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $512万
@@ -22986,7 +23024,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $507万
@@ -22994,7 +23032,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $507万
@@ -23002,7 +23040,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $512万
@@ -23010,7 +23048,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $517万
@@ -23018,7 +23056,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $520万
@@ -23026,7 +23064,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $519万
@@ -23034,7 +23072,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $584万
@@ -23042,7 +23080,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="P13" s="16" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $854万
@@ -23050,7 +23088,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="Q13" s="16" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $658万
@@ -23058,7 +23096,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="R13" s="16" t="inlineStr">
+      <c r="R12" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $490万
@@ -23066,7 +23104,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S13" s="16" t="inlineStr">
+      <c r="S12" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $522万
@@ -23074,7 +23112,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="T13" s="16" t="inlineStr">
+      <c r="T12" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $541万
@@ -23082,7 +23120,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U13" s="16" t="inlineStr">
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $521万
@@ -23090,7 +23128,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="V13" s="16" t="inlineStr">
+      <c r="V12" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $535万
@@ -23099,13 +23137,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $849万
@@ -23113,7 +23151,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $807万
@@ -23121,7 +23159,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $547万
@@ -23129,7 +23167,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $819万
@@ -23137,7 +23175,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $543万
@@ -23145,7 +23183,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $483万
@@ -23153,7 +23191,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $511万
@@ -23161,7 +23199,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $506万
@@ -23169,7 +23207,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $498万
@@ -23177,7 +23215,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $503万
@@ -23185,7 +23223,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $516万
@@ -23193,7 +23231,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $518万
@@ -23201,7 +23239,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $517万
@@ -23209,7 +23247,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O14" s="16" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $582万
@@ -23217,7 +23255,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="P14" s="16" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $851万
@@ -23225,7 +23263,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="Q14" s="16" t="inlineStr">
+      <c r="Q13" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $656万
@@ -23233,7 +23271,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="R14" s="16" t="inlineStr">
+      <c r="R13" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $489万
@@ -23241,7 +23279,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S14" s="16" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $521万
@@ -23249,7 +23287,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T14" s="16" t="inlineStr">
+      <c r="T13" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $539万
@@ -23257,7 +23295,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U14" s="16" t="inlineStr">
+      <c r="U13" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $520万
@@ -23265,7 +23303,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="V14" s="16" t="inlineStr">
+      <c r="V13" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $534万
@@ -23274,13 +23312,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $824万
@@ -23288,7 +23326,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $776万
@@ -23296,7 +23334,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $546万
@@ -23304,7 +23342,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $816万
@@ -23312,7 +23350,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $541万
@@ -23320,7 +23358,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $482万
@@ -23328,7 +23366,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $518万
@@ -23336,7 +23374,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $513万
@@ -23344,7 +23382,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $496万
@@ -23352,7 +23390,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $493万
@@ -23360,7 +23398,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $514万
@@ -23368,7 +23406,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $517万
@@ -23376,7 +23414,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $516万
@@ -23384,7 +23422,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $580万
@@ -23392,7 +23430,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="P14" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $821万
@@ -23400,7 +23438,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="Q14" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $654万
@@ -23408,7 +23446,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="R14" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $498万
@@ -23416,7 +23454,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="S15" s="16" t="inlineStr">
+      <c r="S14" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $519万
@@ -23424,7 +23462,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T15" s="16" t="inlineStr">
+      <c r="T14" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $537万
@@ -23432,7 +23470,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U15" s="16" t="inlineStr">
+      <c r="U14" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $518万
@@ -23440,7 +23478,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="V15" s="16" t="inlineStr">
+      <c r="V14" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $524万
@@ -23449,13 +23487,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $835万
@@ -23463,7 +23501,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $773万
@@ -23471,7 +23509,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $544万
@@ -23479,7 +23517,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $814万
@@ -23487,7 +23525,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $552万
@@ -23495,7 +23533,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $489万
@@ -23503,7 +23541,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $516万
@@ -23511,7 +23549,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $511万
@@ -23519,7 +23557,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $486万
@@ -23527,7 +23565,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $491万
@@ -23535,7 +23573,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $513万
@@ -23543,7 +23581,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $515万
@@ -23551,7 +23589,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $514万
@@ -23559,7 +23597,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $578万
@@ -23567,7 +23605,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="P16" s="16" t="inlineStr">
+      <c r="P15" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $846万
@@ -23575,7 +23613,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="Q16" s="16" t="inlineStr">
+      <c r="Q15" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $663万
@@ -23583,7 +23621,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="R16" s="16" t="inlineStr">
+      <c r="R15" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $497万
@@ -23591,7 +23629,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="S16" s="16" t="inlineStr">
+      <c r="S15" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $518万
@@ -23599,7 +23637,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T16" s="16" t="inlineStr">
+      <c r="T15" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $536万
@@ -23607,7 +23645,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U16" s="16" t="inlineStr">
+      <c r="U15" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $517万
@@ -23615,7 +23653,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="V16" s="16" t="inlineStr">
+      <c r="V15" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $522万
@@ -23624,13 +23662,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $819万
@@ -23638,7 +23676,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $769万
@@ -23646,7 +23684,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $541万
@@ -23654,7 +23692,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $809万
@@ -23662,7 +23700,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $538万
@@ -23670,7 +23708,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $503万
@@ -23678,7 +23716,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $525万
@@ -23686,7 +23724,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $520万
@@ -23694,7 +23732,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $502万
@@ -23702,7 +23740,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $507万
@@ -23710,7 +23748,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $500万
@@ -23718,7 +23756,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $502万
@@ -23726,7 +23764,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $513万
@@ -23734,7 +23772,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $577万
@@ -23742,7 +23780,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="P17" s="16" t="inlineStr">
+      <c r="P16" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $816万
@@ -23750,7 +23788,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="Q17" s="16" t="inlineStr">
+      <c r="Q16" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $661万
@@ -23758,7 +23796,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="R17" s="16" t="inlineStr">
+      <c r="R16" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $485万
@@ -23766,7 +23804,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="S17" s="16" t="inlineStr">
+      <c r="S16" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $516万
@@ -23774,7 +23812,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T17" s="16" t="inlineStr">
+      <c r="T16" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $534万
@@ -23782,7 +23820,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U17" s="16" t="inlineStr">
+      <c r="U16" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $498万
@@ -23790,7 +23828,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="V17" s="16" t="inlineStr">
+      <c r="V16" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $529万
@@ -23799,13 +23837,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $819万
@@ -23813,7 +23851,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $762万
@@ -23821,7 +23859,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $536万
@@ -23829,7 +23867,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $802万
@@ -23837,7 +23875,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $536万
@@ -23845,7 +23883,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $502万
@@ -23853,7 +23891,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $524万
@@ -23861,7 +23899,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $518万
@@ -23869,7 +23907,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $500万
@@ -23877,7 +23915,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $488万
@@ -23885,7 +23923,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $497万
@@ -23893,7 +23931,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $499万
@@ -23901,7 +23939,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $510万
@@ -23909,7 +23947,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $583万
@@ -23917,7 +23955,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="P18" s="16" t="inlineStr">
+      <c r="P17" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $814万
@@ -23925,7 +23963,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="Q18" s="16" t="inlineStr">
+      <c r="Q17" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $659万
@@ -23933,7 +23971,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="R18" s="16" t="inlineStr">
+      <c r="R17" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $494万
@@ -23941,7 +23979,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="S18" s="16" t="inlineStr">
+      <c r="S17" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $514万
@@ -23949,7 +23987,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T18" s="16" t="inlineStr">
+      <c r="T17" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $531万
@@ -23957,7 +23995,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U18" s="16" t="inlineStr">
+      <c r="U17" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $506万
@@ -23965,7 +24003,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="V18" s="16" t="inlineStr">
+      <c r="V17" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $517万
@@ -23974,13 +24012,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $832万
@@ -23988,7 +24026,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $733万
@@ -23996,7 +24034,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $545万
@@ -24004,7 +24042,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $797万
@@ -24012,7 +24050,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $535万
@@ -24020,7 +24058,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $476万
@@ -24028,7 +24066,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $522万
@@ -24036,7 +24074,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $517万
@@ -24044,7 +24082,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $490万
@@ -24052,7 +24090,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $487万
@@ -24060,7 +24098,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $492万
@@ -24068,7 +24106,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $496万
@@ -24076,7 +24114,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $507万
@@ -24084,7 +24122,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $570万
@@ -24092,7 +24130,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="P19" s="16" t="inlineStr">
+      <c r="P18" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $811万
@@ -24100,7 +24138,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q19" s="16" t="inlineStr">
+      <c r="Q18" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $679万
@@ -24108,7 +24146,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="R19" s="16" t="inlineStr">
+      <c r="R18" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $482万
@@ -24116,7 +24154,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="S19" s="16" t="inlineStr">
+      <c r="S18" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $513万
@@ -24124,7 +24162,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="T19" s="16" t="inlineStr">
+      <c r="T18" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $527万
@@ -24132,7 +24170,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U19" s="16" t="inlineStr">
+      <c r="U18" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $492万
@@ -24140,7 +24178,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="V19" s="16" t="inlineStr">
+      <c r="V18" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $514万
@@ -24149,13 +24187,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $827万
@@ -24163,7 +24201,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $768万
@@ -24171,7 +24209,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $543万
@@ -24179,7 +24217,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $795万
@@ -24187,7 +24225,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $533万
@@ -24195,7 +24233,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $475万
@@ -24203,7 +24241,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $521万
@@ -24211,7 +24249,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $515万
@@ -24219,7 +24257,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $481万
@@ -24227,7 +24265,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $486万
@@ -24235,7 +24273,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $500万
@@ -24243,7 +24281,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $510万
@@ -24251,7 +24289,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $504万
@@ -24259,7 +24297,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O20" s="16" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $566万
@@ -24267,7 +24305,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="P20" s="16" t="inlineStr">
+      <c r="P19" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $809万
@@ -24275,7 +24313,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="Q20" s="16" t="inlineStr">
+      <c r="Q19" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $644万
@@ -24283,7 +24321,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="R20" s="16" t="inlineStr">
+      <c r="R19" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $480万
@@ -24291,7 +24329,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="S20" s="16" t="inlineStr">
+      <c r="S19" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $511万
@@ -24299,7 +24337,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="T20" s="16" t="inlineStr">
+      <c r="T19" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $524万
@@ -24307,7 +24345,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U20" s="16" t="inlineStr">
+      <c r="U19" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $489万
@@ -24315,7 +24353,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="V20" s="16" t="inlineStr">
+      <c r="V19" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $530万
@@ -24324,13 +24362,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $825万
@@ -24338,7 +24376,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $765万
@@ -24346,7 +24384,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $547万
@@ -24354,7 +24392,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $793万
@@ -24362,7 +24400,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $528万
@@ -24370,7 +24408,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $473万
@@ -24378,7 +24416,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $509万
@@ -24386,7 +24424,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $504万
@@ -24394,7 +24432,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $493万
@@ -24402,7 +24440,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $498万
@@ -24410,7 +24448,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $499万
@@ -24418,7 +24456,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $508万
@@ -24426,7 +24464,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $503万
@@ -24434,7 +24472,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $565万
@@ -24442,7 +24480,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="P21" s="16" t="inlineStr">
+      <c r="P20" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $833万
@@ -24450,7 +24488,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="Q21" s="16" t="inlineStr">
+      <c r="Q20" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $657万
@@ -24458,7 +24496,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="R21" s="16" t="inlineStr">
+      <c r="R20" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $479万
@@ -24466,7 +24504,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="S21" s="16" t="inlineStr">
+      <c r="S20" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $504万
@@ -24474,7 +24512,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="T21" s="16" t="inlineStr">
+      <c r="T20" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $523万
@@ -24482,7 +24520,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U21" s="16" t="inlineStr">
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $496万
@@ -24490,7 +24528,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="V21" s="16" t="inlineStr">
+      <c r="V20" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $528万
@@ -24499,13 +24537,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $782万
@@ -24513,7 +24551,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $738万
@@ -24521,7 +24559,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $546万
@@ -24529,7 +24567,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $790万
@@ -24537,7 +24575,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $521万
@@ -24545,7 +24583,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $472万
@@ -24553,7 +24591,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $507万
@@ -24561,7 +24599,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $503万
@@ -24569,7 +24607,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $486万
@@ -24577,7 +24615,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $483万
@@ -24585,7 +24623,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $497万
@@ -24593,7 +24631,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $507万
@@ -24601,7 +24639,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $501万
@@ -24609,7 +24647,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $563万
@@ -24617,7 +24655,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="P22" s="16" t="inlineStr">
+      <c r="P21" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $831万
@@ -24625,7 +24663,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="Q21" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $641万
@@ -24633,7 +24671,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="R22" s="16" t="inlineStr">
+      <c r="R21" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $477万
@@ -24641,7 +24679,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="S22" s="16" t="inlineStr">
+      <c r="S21" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $508万
@@ -24649,7 +24687,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="T22" s="16" t="inlineStr">
+      <c r="T21" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $521万
@@ -24657,7 +24695,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U22" s="16" t="inlineStr">
+      <c r="U21" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $486万
@@ -24665,7 +24703,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="V22" s="16" t="inlineStr">
+      <c r="V21" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $526万
@@ -24674,13 +24712,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $822万
@@ -24688,7 +24726,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $748万
@@ -24696,7 +24734,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $526万
@@ -24704,7 +24742,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $814万
@@ -24712,7 +24750,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $519万
@@ -24720,7 +24758,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $470万
@@ -24728,7 +24766,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $506万
@@ -24736,7 +24774,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $501万
@@ -24744,7 +24782,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $476万
@@ -24752,7 +24790,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $481万
@@ -24760,7 +24798,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $495万
@@ -24768,7 +24806,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $505万
@@ -24776,7 +24814,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $499万
@@ -24784,7 +24822,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O23" s="16" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $571万
@@ -24792,7 +24830,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="P23" s="16" t="inlineStr">
+      <c r="P22" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $828万
@@ -24800,7 +24838,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q23" s="16" t="inlineStr">
+      <c r="Q22" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $653万
@@ -24808,7 +24846,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="R23" s="16" t="inlineStr">
+      <c r="R22" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $476万
@@ -24816,7 +24854,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="S23" s="16" t="inlineStr">
+      <c r="S22" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $501万
@@ -24824,7 +24862,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="T23" s="16" t="inlineStr">
+      <c r="T22" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $519万
@@ -24832,7 +24870,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="U23" s="16" t="inlineStr">
+      <c r="U22" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $484万
@@ -24840,7 +24878,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="V23" s="16" t="inlineStr">
+      <c r="V22" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $525万
@@ -24849,13 +24887,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $782万
@@ -24863,7 +24901,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $761万
@@ -24871,7 +24909,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $526万
@@ -24879,7 +24917,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $814万
@@ -24887,7 +24925,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $519万
@@ -24895,7 +24933,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $470万
@@ -24903,7 +24941,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $498万
@@ -24911,7 +24949,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $493万
@@ -24919,7 +24957,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $476万
@@ -24927,7 +24965,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $481万
@@ -24935,7 +24973,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $495万
@@ -24943,7 +24981,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $505万
@@ -24951,7 +24989,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N24" s="16" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $499万
@@ -24959,7 +24997,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="O24" s="16" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $561万
@@ -24967,7 +25005,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="P24" s="16" t="inlineStr">
+      <c r="P23" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $828万
@@ -24975,7 +25013,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="Q24" s="16" t="inlineStr">
+      <c r="Q23" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $650万
@@ -24983,7 +25021,7 @@
 (24年-08月)</t>
         </is>
       </c>
-      <c r="R24" s="16" t="inlineStr">
+      <c r="R23" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $476万
@@ -24991,7 +25029,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="S24" s="16" t="inlineStr">
+      <c r="S23" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $490万
@@ -24999,7 +25037,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="T24" s="16" t="inlineStr">
+      <c r="T23" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $519万
@@ -25007,7 +25045,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U24" s="16" t="inlineStr">
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $484万
@@ -25015,7 +25053,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="V24" s="16" t="inlineStr">
+      <c r="V23" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $525万
@@ -25024,13 +25062,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $822万
@@ -25038,7 +25076,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $756万
@@ -25046,7 +25084,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $541万
@@ -25054,7 +25092,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $810万
@@ -25062,7 +25100,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $518万
@@ -25070,7 +25108,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $469万
@@ -25078,7 +25116,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $496万
@@ -25086,7 +25124,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $492万
@@ -25094,7 +25132,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $475万
@@ -25102,7 +25140,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $480万
@@ -25110,7 +25148,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $483万
@@ -25118,7 +25156,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $487万
@@ -25126,7 +25164,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $498万
@@ -25134,7 +25172,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O25" s="16" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $571万
@@ -25142,7 +25180,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="P25" s="16" t="inlineStr">
+      <c r="P24" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $801万
@@ -25150,7 +25188,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q25" s="16" t="inlineStr">
+      <c r="Q24" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $648万
@@ -25158,7 +25196,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="R25" s="16" t="inlineStr">
+      <c r="R24" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $485万
@@ -25166,7 +25204,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="S25" s="16" t="inlineStr">
+      <c r="S24" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $488万
@@ -25174,7 +25212,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="T25" s="16" t="inlineStr">
+      <c r="T24" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $518万
@@ -25182,7 +25220,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U25" s="16" t="inlineStr">
+      <c r="U24" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $483万
@@ -25190,7 +25228,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="V25" s="16" t="inlineStr">
+      <c r="V24" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $523万
@@ -25199,13 +25237,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 417呎 (2房)
 $820万
@@ -25213,7 +25251,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 369呎 (1房)
 $739万
@@ -25221,7 +25259,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $520万
@@ -25229,7 +25267,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
 $813万
@@ -25237,7 +25275,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $514万
@@ -25245,7 +25283,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $474万
@@ -25253,7 +25291,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 262呎 (1房)
 $493万
@@ -25261,7 +25299,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 262呎 (1房)
 $489万
@@ -25269,7 +25307,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 262呎 (1房)
 $473万
@@ -25277,7 +25315,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 262呎 (1房)
 $477万
@@ -25285,7 +25323,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L26" s="16" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 266呎 (1房)
 $480万
@@ -25293,7 +25331,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $484万
@@ -25301,7 +25339,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N26" s="16" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $496万
@@ -25309,7 +25347,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O26" s="16" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>P | 314呎 (1房)
 $561万
@@ -25317,7 +25355,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="P26" s="16" t="inlineStr">
+      <c r="P25" s="20" t="inlineStr">
         <is>
           <t>Q | 430呎 (3房)
 $801万
@@ -25325,7 +25363,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="Q26" s="16" t="inlineStr">
+      <c r="Q25" s="20" t="inlineStr">
         <is>
           <t>R | 346呎 (2房)
 $646万
@@ -25333,7 +25371,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="R26" s="16" t="inlineStr">
+      <c r="R25" s="20" t="inlineStr">
         <is>
           <t>S | 269呎 (1房)
 $473万
@@ -25341,7 +25379,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="S26" s="16" t="inlineStr">
+      <c r="S25" s="20" t="inlineStr">
         <is>
           <t>T | 263呎 (1房)
 $487万
@@ -25349,7 +25387,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="T26" s="16" t="inlineStr">
+      <c r="T25" s="20" t="inlineStr">
         <is>
           <t>U | 262呎 (1房)
 $527万
@@ -25357,7 +25395,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="U26" s="16" t="inlineStr">
+      <c r="U25" s="20" t="inlineStr">
         <is>
           <t>V | 262呎 (1房)
 $490万
@@ -25365,7 +25403,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="V26" s="16" t="inlineStr">
+      <c r="V25" s="20" t="inlineStr">
         <is>
           <t>W | 270呎 (1房)
 $522万
@@ -25374,13 +25412,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 379呎 (2房)
 $940万
@@ -25388,7 +25426,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 331呎 (1房)
 $828万
@@ -25396,7 +25434,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 246呎 (1房)
 $635万
@@ -25404,7 +25442,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 373呎 (2房)
 $910万
@@ -25412,7 +25450,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 239呎 (1房)
 $586万
@@ -25420,7 +25458,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 228呎 (1房)
 $554万
@@ -25428,7 +25466,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 225呎 (1房)
 $528万
@@ -25436,7 +25474,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 225呎 (1房)
 $538万
@@ -25444,7 +25482,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 225呎 (1房)
 $538万
@@ -25452,7 +25490,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 225呎 (1房)
 $544万
@@ -25460,7 +25498,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 228呎 (1房)
 $523万
@@ -25468,7 +25506,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 228呎 (1房)
 $538万
@@ -25476,7 +25514,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>N | 223呎 (1房)
 $546万
@@ -25484,7 +25522,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="O27" s="16" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>P | 276呎 (1房)
 $701万
@@ -25492,7 +25530,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="P27" s="16" t="inlineStr">
+      <c r="P26" s="20" t="inlineStr">
         <is>
           <t>Q | 392呎 (3房)
 $980万
@@ -25500,7 +25538,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="Q27" s="16" t="inlineStr">
+      <c r="Q26" s="20" t="inlineStr">
         <is>
           <t>R | 309呎 (2房)
 $779万
@@ -25508,7 +25546,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="R27" s="16" t="inlineStr">
+      <c r="R26" s="20" t="inlineStr">
         <is>
           <t>S | 229呎 (1房)
 $614万
@@ -25516,7 +25554,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="S27" s="16" t="inlineStr">
+      <c r="S26" s="20" t="inlineStr">
         <is>
           <t>T | 225呎 (1房)
 $578万
@@ -25524,7 +25562,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="T27" s="16" t="inlineStr">
+      <c r="T26" s="20" t="inlineStr">
         <is>
           <t>U | 224呎 (1房)
 $573万
@@ -25532,7 +25570,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="U27" s="16" t="inlineStr">
+      <c r="U26" s="20" t="inlineStr">
         <is>
           <t>V | 224呎 (1房)
 $571万
@@ -25540,7 +25578,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="V27" s="16" t="inlineStr">
+      <c r="V26" s="20" t="inlineStr">
         <is>
           <t>W | 233呎 (1房)
 $580万
@@ -25551,7 +25589,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
